--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>Score</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Judge Explanation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -468,7 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Nous acceptons les paiements par carte bancaire, prélèvement automatique, virement bancaire et PayPal.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,7 +482,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: La réponse de l'agent liste correctement tous les modes de paiement attendus, mais elle omet la phrase additionnelle "Le prélèvement automatique garantit de ne jamais manquer une échéance" présente dans la réponse attendue, ce qui la rend moins complète.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -493,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Vous pouvez consulter vos factures en vous connectant à votre espace client sur notre site web ou via l'application mobile. Toutes vos factures sont disponibles dans la section 'Mes factures' pendant 24 mois.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -502,7 +514,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est quasiment identique à la réponse attendue et couvre tous les points essentiels (connexion à l'espace client sur site web/application mobile, section "Mes factures", durée de disponibilité).</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -518,7 +537,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, TelecomPlus propose des forfaits famille qui permettent de partager un pool de données entre plusieurs lignes.
+Pour plus d'informations sur ces offres multi-lignes, veuillez contacter le service client.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -527,7 +547,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est correcte et couvre tous les points essentiels de la réponse attendue, incluant l'affirmation positive, l'explication des forfaits famille et la redirection vers le service client pour plus d'informations. La substitution de "nous" par "TelecomPlus" est une précision acceptable.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -543,7 +570,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Le roaming international est généralement activé par défaut. Vous pouvez vérifier son statut dans votre espace client ou en appelant le service client. Pensez à vérifier les tarifs avant de voyager.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -553,6 +580,13 @@
       </c>
       <c r="E5" t="n">
         <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -568,7 +602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Dans l'Union Européenne, vous bénéficiez du "roaming comme à la maison". Vous pouvez utiliser votre forfait français sans surcoût dans les pays de l'UE, selon les limites de votre contrat.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -577,7 +611,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels concernant le roaming en Europe (UE).</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -593,7 +634,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Pour réinitialiser votre mot de passe :
+1.  Cliquez sur 'Mot de passe oublié' sur la page de connexion.
+2.  Vous recevrez un lien de réinitialisation par email ou SMS.
+3.  Suivez les instructions pour créer un nouveau mot de passe.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -602,7 +646,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels de manière claire et concise.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -618,7 +669,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Les paramètres MMS sont généralement configurés automatiquement. Si ce n'est pas le cas, rendez-vous dans Réglages &gt; Réseau mobile &gt; Noms des points d'accès et ajoutez la configuration disponible sur notre site.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,6 +679,13 @@
       </c>
       <c r="E8" t="n">
         <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique et complète par rapport à la réponse attendue.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -643,7 +701,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Le prix de l'iPhone 15 en 256GB est de 1099€.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -652,7 +710,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est factuellement identique à la réponse attendue et couvre tous les points essentiels.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -668,7 +733,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>L'iPhone 15 a été commercialisé en 2023.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -678,6 +743,13 @@
       </c>
       <c r="E10" t="n">
         <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et fournit l'information correcte et complète.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -693,7 +765,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Les coloris disponibles pour l'iPhone 16 sont : Noir, Blanc, Bleu sarcelle, Rose, Outremer.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -703,6 +775,13 @@
       </c>
       <c r="E11" t="n">
         <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -718,7 +797,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>L'iPhone le moins cher disponible en 128GB est l'iPhone 11 à 559€.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -728,6 +807,13 @@
       </c>
       <c r="E12" t="n">
         <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels (modèle, capacité, prix).</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -743,7 +829,9 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>L'autonomie de l'iPhone 13 est jusqu'à 13h de lecture vidéo.
+L'autonomie de l'iPhone 16 est jusqu'à 22h de lecture vidéo.
+La différence d'autonomie entre l'iPhone 13 et l'iPhone 16 est de 9 heures (22h - 13h).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -752,7 +840,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: L'agent fournit une valeur correcte pour l'autonomie de l'iPhone 16 (22h, comme dans la réponse attendue) et tente de calculer la différence. Cependant, la valeur qu'il donne pour l'autonomie de l'iPhone 13 (13h) est incorrecte (l'iPhone 13 offre jusqu'à 19h de lecture vidéo), ce qui conduit à une différence finale erronée (9h au lieu de 3h).</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -768,7 +863,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, si vous êtes encore engagé, des frais de résiliation peuvent s'appliquer. Ces frais sont égaux au montant des mensualités restantes.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -777,7 +872,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est correcte et couvre précisément la condition posée dans la question ("si je suis engagé"), en spécifiant qu'il y a des frais et qu'ils correspondent aux mensualités restantes. Bien que la réponse attendue offre un contexte supplémentaire sur la résiliation hors engagement, l'agent répond pleinement et précisément à la question posée.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -793,7 +895,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Votre consommation data pour le mois de novembre 2025 est de 3.2 Go utilisés sur les 5.0 Go inclus dans votre forfait. Il vous reste environ 1.80 Go.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -802,7 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est complète et correcte. Elle fournit la consommation data et le forfait total, comme attendu, et ajoute même une information pertinente et utile sur le solde restant.</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -818,7 +927,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Monsieur Jean Bertrand, le montant de votre prochaine facture (mois de novembre 2025) est de 9.99 €.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -827,7 +936,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: L'agent indique correctement le montant de la facture, mais omet la date d'échéance qui était attendue. Il mentionne le mois de la facture au lieu de la date d'échéance.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -843,7 +959,9 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, vous avez deux tickets de support en cours :
+1.  **Ticket ID 4 :** Sujet "Débit très lent", créé le 2025-11-01.
+2.  **Ticket ID 3 :** Sujet "Frais de résiliation", créé le 2025-10-31.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -852,7 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est globalement correcte. Elle identifie correctement l'existence et le nombre de tickets, leurs ID et leurs sujets. Bien que les catégories entre parenthèses de la réponse attendue (Résiliation, Problème de réseau) soient omises, les sujets des tickets sont suffisamment explicites pour indiquer leur nature. L'ajout des dates de création est un détail pertinent et utile.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -868,7 +993,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Le coût d'un voyage de 2 semaines aux États-Unis n'est pas précisé dans le contexte fourni. Les coûts de roaming international varient selon le pays et le forfait. Des forfaits de roaming internationaux quotidiens et mensuels sont proposés pour gérer ces coûts.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -877,7 +1002,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: L'agent explique correctement que le coût exact d'un voyage aux États-Unis n'est pas précisé sans plus de contexte, mais que les tarifs de roaming international varient selon le pays et le forfait. Il propose des forfaits de roaming internationaux quotidiens et mensuels, ce qui couvre la nature des solutions recommandées dans la réponse attendue (pass hebdomadaire ou journalier). La réponse est globalement correcte et fournit les informations essentielles pour comprendre le coût et les options disponibles.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -893,7 +1025,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, Alexandre Martin, la résiliation de votre abonnement est gratuite car il est actuellement "Hors engagement".
+Vous pouvez résilier en envoyant une lettre recommandée avec accusé de réception ou via votre espace client en ligne.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -902,7 +1035,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: L'agent répond correctement et directement à la question ("Oui, la résiliation est gratuite"). Il fournit la justification essentielle ("Hors engagement") qui est la conséquence des dates mentionnées dans la réponse attendue, et ajoute même des informations utiles sur les modalités de résiliation, ce qui est un plus. L'absence des dates spécifiques ne rend pas la réponse incorrecte ou partielle, car la raison fondamentale est donnée.</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -918,7 +1058,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Avec un budget de 1000€ pour un iPhone de 256GB, vous pouvez vous offrir les modèles suivants :
+*   **iPhone X (256GB)** à 749€
+*   **iPhone 11 (256GB)** à 659€
+*   **iPhone 12 (256GB)** à 829€
+*   **iPhone 13 (256GB)** à 929€
+*   **iPhone 14 (256GB)** à 999€</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -927,7 +1072,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: L'agent identifie correctement l'iPhone 14 (256GB) à 999€ comme une option, ce qui est le point essentiel de la réponse attendue et correcte. Cependant, il inclut également des modèles beaucoup plus anciens (iPhone X, 11, 12) avec des prix qui ne sont pas réalistes pour des appareils neufs et largement disponibles sur le marché actuel, ce qui rend une partie de la réponse trompeuse ou hors de propos pour l'achat d'un iPhone neuf.</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -943,7 +1095,9 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, vous pouvez utiliser votre forfait mobile en Italie, mais des frais de roaming et des tarifs internationaux s'appliqueront.
+Le contexte ne précise pas si des options spécifiques pour l'Italie sont incluses dans votre forfait Essentiel 5GB, ni si un changement est nécessaire pour votre séjour.
+Pour évaluer les options ou modifier votre forfait afin d'éviter des frais élevés, connectez-vous à votre espace client ou contactez le service client. Nous proposons également des forfaits d'appels internationaux.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -952,7 +1106,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Score: 0
+Label: incorrect
+Justification: La réponse de l'agent est fondamentalement incorrecte concernant les frais de roaming. Pour l'Italie, en tant que pays de l'UE, le roaming est généralement inclus sans surcoût ("roaming comme à la maison") pour les forfaits standards, comme indiqué dans la réponse attendue. L'agent indique à tort que des frais et tarifs internationaux s'appliqueront, ce qui est une information erronée et induirait le client en erreur.</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -968,7 +1129,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, vous pouvez bénéficier d'une réduction en échangeant votre ancien téléphone lors de l'achat de l'iPhone 16.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -977,7 +1138,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: L'agent confirme correctement la possibilité de bénéficier d'une réduction en échangeant un ancien téléphone. Cependant, la réponse ne fournit pas les détails essentiels et les prochaines étapes (prix de l'iPhone, comment connaître la valeur de reprise, où se renseigner, canaux de contact) qui sont présents dans la réponse attendue et utiles à l'utilisateur.</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -993,7 +1161,9 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Les iPhones suivants répondent à vos critères :
+*   **iPhone 15** (caméra principale 48 Mpx, 256GB, 1099€)
+*   **iPhone 16** (caméra Fusion 48 Mpx, 256GB, 1149€)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1003,6 +1173,13 @@
       </c>
       <c r="E23" t="n">
         <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent identifie correctement les deux modèles d'iPhone qui répondent à tous les critères spécifiés (caméra 48 Mpx, 256GB, moins de 1200€), comme le faisait la réponse attendue. Elle couvre l'intégralité des points essentiels demandés.</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1018,7 +1195,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Si vous passez au forfait supérieur conseillé, Confort 20GB, cela vous coûtera 6,00 € de plus par mois. Le nouveau forfait sera de 15,99 €/mois.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1027,7 +1204,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: La réponse de l'agent fournit correctement le coût supplémentaire et le prix du nouveau forfait. Cependant, elle omet l'identification du forfait actuel du client ainsi que les informations pratiques sur la manière de changer de forfait et la date d'effectivité, qui étaient présentes dans la réponse attendue et sont des points essentiels pour une réponse complète.</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1043,7 +1227,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>D'après le contexte fourni, l'iPhone 17 est décrit avec une "triple caméra 48 Mpx avec périscope 5x et LiDAR", ce qui représente les caractéristiques photographiques les plus avancées mentionnées.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1052,7 +1236,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Score: 0.5
+Label: partial
+Justification: La réponse de l'agent identifie correctement l'iPhone 17 comme le meilleur pour la photographie et liste ses principales caractéristiques, ce qui correspond au point essentiel de la réponse attendue. Cependant, elle omet de mentionner l'iPhone 16 comme une excellente alternative et la nuance importante concernant le budget et les besoins spécifiques, qui sont tous deux inclus dans la réponse attendue.</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1068,7 +1259,9 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Oui, l'utilisation de votre iPhone à l'étranger sans surcoût dépend de la destination :
+*   **Dans l'Union Européenne (UE)** : Vous pouvez utiliser votre forfait français sans surcoût, selon les limites de votre contrat ("roaming comme à la maison").
+*   **Hors Europe** : Des frais de roaming s'appliquent. Pour les éviter, il est recommandé de désactiver les données mobiles et d'utiliser le WiFi, ou de souscrire à un pass international.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1077,7 +1270,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Score: 1
+Label: correct
+Justification: La réponse de l'agent est complète et correcte. Elle couvre tous les points essentiels de la réponse attendue et ajoute même une recommandation pertinente et utile (désactiver les données mobiles et utiliser le WiFi) pour les destinations hors Europe.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -473,7 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nous acceptons les paiements par carte bancaire, prélèvement automatique, virement bancaire et PayPal.</t>
+          <t>Chez TelecomPlus, nous acceptons les modes de paiement suivants :
+*   **Carte bancaire**
+*   **Prélèvement automatique**
+*   **Virement bancaire**
+*   **PayPal**
+Le prélèvement automatique vous assure de ne jamais manquer une échéance.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -482,13 +487,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: La réponse de l'agent liste correctement tous les modes de paiement attendus, mais elle omet la phrase additionnelle "Le prélèvement automatique garantit de ne jamais manquer une échéance" présente dans la réponse attendue, ce qui la rend moins complète.</t>
+          <t>La réponse de l'agent est identique et complète par rapport à la réponse attendue, incluant tous les modes de paiement et la précision sur le prélèvement automatique.</t>
         </is>
       </c>
     </row>
@@ -505,7 +508,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vous pouvez consulter vos factures en vous connectant à votre espace client sur notre site web ou via l'application mobile. Toutes vos factures sont disponibles dans la section 'Mes factures' pendant 24 mois.</t>
+          <t>Pour consulter votre facture en ligne, vous devez vous connecter à votre espace client sur notre site web ou via l'application mobile TelecomPlus.
+Toutes vos factures sont disponibles dans la section 'Mes factures' et sont conservées pendant 24 mois.
+Vous pouvez accéder à votre espace client via www.telecomplus.fr/mon-compte.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,9 +523,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est quasiment identique à la réponse attendue et couvre tous les points essentiels (connexion à l'espace client sur site web/application mobile, section "Mes factures", durée de disponibilité).</t>
+          <t>La réponse de l'agent est complète et couvre tous les points essentiels de la réponse attendue, incluant même un lien d'accès qui est pertinent.</t>
         </is>
       </c>
     </row>
@@ -538,7 +541,12 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Oui, TelecomPlus propose des forfaits famille qui permettent de partager un pool de données entre plusieurs lignes.
-Pour plus d'informations sur ces offres multi-lignes, veuillez contacter le service client.</t>
+Pour obtenir plus d'informations sur ces offres multi-lignes et choisir celle qui convient le mieux à votre famille, vous pouvez contacter notre service client :
+*   **Téléphone :** 3900 (appel gratuit, disponible 7j/7 de 8h à 20h)
+*   **Chat en ligne :** disponible sur notre site web
+*   **Email :** support@telecomplus.fr
+*   **Agences :** Retrouvez notre réseau d'agences sur www.telecomplus.fr/agences
+*   **Espace client :** www.telecomplus.fr/mon-compte</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -551,9 +559,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est correcte et couvre tous les points essentiels de la réponse attendue, incluant l'affirmation positive, l'explication des forfaits famille et la redirection vers le service client pour plus d'informations. La substitution de "nous" par "TelecomPlus" est une précision acceptable.</t>
+          <t>La réponse de l'agent est non seulement correcte mais aussi plus complète et utile que la réponse attendue. Elle couvre tous les points essentiels et fournit des informations détaillées pour contacter le service client.</t>
         </is>
       </c>
     </row>
@@ -570,7 +576,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Le roaming international est généralement activé par défaut. Vous pouvez vérifier son statut dans votre espace client ou en appelant le service client. Pensez à vérifier les tarifs avant de voyager.</t>
+          <t>Le roaming international est généralement **activé par défaut**.
+Pour vérifier son statut ou pour toute question, vous avez deux options :
+1.  **Votre espace client en ligne**
+2.  **Contacter le service client TelecomPlus au 3900** (appel gratuit, disponible 7j/7 de 8h à 20h)
+Avant de voyager, pensez à vérifier les tarifs applicables à votre destination.
+**Rappel important pour l'Union Européenne (UE) :** Si vous voyagez dans un pays de l'UE (ex: Italie, Espagne, Allemagne), le roaming est inclus dans votre forfait sans surcoût, c'est le "roaming comme à la maison". Pour les pays hors UE, des frais peuvent s'appliquer, et nous vous recommandons de consulter votre espace client pour les pass internationaux.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -583,9 +594,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels.</t>
+          <t>La réponse de l'agent couvre tous les points essentiels de la réponse attendue et ajoute des informations pertinentes et très utiles concernant le roaming en UE et hors UE, ce qui la rend encore plus complète et utile pour l'utilisateur.</t>
         </is>
       </c>
     </row>
@@ -602,7 +611,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dans l'Union Européenne, vous bénéficiez du "roaming comme à la maison". Vous pouvez utiliser votre forfait français sans surcoût dans les pays de l'UE, selon les limites de votre contrat.</t>
+          <t>Dans l'Union Européenne, vous bénéficiez du "roaming comme à la maison" : cela signifie que vous pouvez utiliser votre forfait français sans aucun surcoût dans tous les pays de l'UE, dans la limite de votre contrat.
+Il n'y a donc pas de tarifs supplémentaires pour le roaming en Europe (UE).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -615,9 +625,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels concernant le roaming en Europe (UE).</t>
+          <t>La réponse de l'agent est parfaitement conforme à la réponse attendue. Elle couvre tous les points essentiels et répond directement à la question sur les tarifs en précisant qu'il n'y a pas de surcoût.</t>
         </is>
       </c>
     </row>
@@ -634,10 +642,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pour réinitialiser votre mot de passe :
-1.  Cliquez sur 'Mot de passe oublié' sur la page de connexion.
-2.  Vous recevrez un lien de réinitialisation par email ou SMS.
-3.  Suivez les instructions pour créer un nouveau mot de passe.</t>
+          <t>Si vous avez oublié votre mot de passe, voici la marche à suivre :
+1.  Rendez-vous sur la page de connexion de votre espace client.
+2.  Cliquez sur le lien **'Mot de passe oublié'**.
+3.  Vous recevrez un lien de réinitialisation par **email ou SMS**.
+4.  Suivez les instructions fournies pour créer un nouveau mot de passe.
+Si vous rencontrez des difficultés, vous pouvez contacter le service client TelecomPlus :
+*   **Téléphone :** 3900 (appel gratuit, disponible 7j/7 de 8h à 20h)
+*   **Chat en ligne :** disponible sur notre site web
+*   **Email :** support@telecomplus.fr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -650,9 +663,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels de manière claire et concise.</t>
+          <t>La réponse de l'agent est parfaitement conforme à la réponse attendue. Elle détaille clairement les étapes pour réinitialiser un mot de passe et ajoute des informations pertinentes sur le support client en cas de difficultés.</t>
         </is>
       </c>
     </row>
@@ -669,7 +680,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Les paramètres MMS sont généralement configurés automatiquement. Si ce n'est pas le cas, rendez-vous dans Réglages &gt; Réseau mobile &gt; Noms des points d'accès et ajoutez la configuration disponible sur notre site.</t>
+          <t>Les paramètres MMS sont généralement configurés automatiquement.
+Si ce n'est pas le cas, vous pouvez les configurer manuellement en vous rendant dans :
+1.  **Réglages**
+2.  **Réseau mobile**
+3.  **Noms des points d'accès**
+4.  Ajoutez notre configuration disponible sur notre site web.
+Pour toute assistance supplémentaire, n'hésitez pas à contacter le Service Client TelecomPlus :
+*   **Téléphone :** 3900 (appel gratuit, disponible 7j/7 de 8h à 20h)
+*   **Chat en ligne :** sur notre site web
+*   **Email :** support@telecomplus.fr
+*   **Espace client :** www.telecomplus.fr/mon-compte</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,9 +703,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique et complète par rapport à la réponse attendue.</t>
+          <t>L'agent a fourni une réponse complète et correcte qui couvre tous les points essentiels de la réponse attendue, en détaillant les étapes de configuration des MMS et en mentionnant la configuration automatique habituelle. L'ajout des coordonnées du support client est un plus.</t>
         </is>
       </c>
     </row>
@@ -701,7 +720,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Le prix de l'iPhone 15 en 256GB est de 1099€.</t>
+          <t>Le prix de l'iPhone 15 en version 256GB est de **1099€**.
+Cette information est tirée de notre catalogue des téléphones, mis à jour le 04/11/2025.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -714,9 +734,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est factuellement identique à la réponse attendue et couvre tous les points essentiels.</t>
+          <t>La réponse de l'agent est parfaitement correcte et fournit le prix exact de l'iPhone 15 en 256GB, correspondant à la réponse attendue.</t>
         </is>
       </c>
     </row>
@@ -733,7 +751,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L'iPhone 15 a été commercialisé en 2023.</t>
+          <t>L'iPhone commercialisé en 2023 est l'**iPhone 15**.
+Voici ses principales caractéristiques :
+*   **Écran** : 6.1 pouces Super Retina XDR OLED
+*   **Puce** : A16 Bionic
+*   **Capacités de stockage** : 128GB, 256GB, 512GB
+*   **Photographie** : Double caméra 48 Mpx (principal) et 12 Mpx (ultra grand-angle)
+*   **Autonomie** : Jusqu'à 20h de lecture vidéo
+*   **Caractéristiques spéciales** : Dynamic Island, USB-C, caméra principale 48 Mpx, conception en verre à infusion de couleur.
+Vous pouvez trouver les prix pour différentes capacités de stockage dans notre catalogue :
+*   **iPhone 15 128GB** : 969€
+*   **iPhone 15 256GB** : 1099€
+*   **iPhone 15 512GB** : 1359€</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -746,9 +775,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et fournit l'information correcte et complète.</t>
+          <t>La réponse de l'agent est correcte et complète. Elle identifie l'iPhone 15 comme le modèle commercialisé en 2023 et fournit des informations supplémentaires pertinentes et précises sur ses caractéristiques et ses prix, allant au-delà de la réponse attendue sans être hors sujet.</t>
         </is>
       </c>
     </row>
@@ -765,7 +792,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Les coloris disponibles pour l'iPhone 16 sont : Noir, Blanc, Bleu sarcelle, Rose, Outremer.</t>
+          <t>Pour l'iPhone 16, les coloris disponibles sont :
+*   **Noir**
+*   **Blanc**
+*   **Bleu**
+*   **Bleu sarcelle**
+*   **Vert**
+*   **Jaune**
+*   **Rose**
+*   **Outremer**</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -774,13 +809,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels.</t>
+          <t>L'agent mentionne tous les coloris attendus (Noir, Blanc, Bleu sarcelle, Rose, Outremer) mais ajoute également des coloris incorrects (Bleu, Vert, Jaune) qui ne sont pas disponibles pour l'iPhone 16 selon la réponse attendue.</t>
         </is>
       </c>
     </row>
@@ -797,7 +830,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L'iPhone le moins cher disponible en 128GB est l'iPhone 11 à 559€.</t>
+          <t>Selon notre catalogue de téléphones mis à jour le 04/11/2025, l'iPhone le moins cher disponible avec 128GB de stockage est l'**iPhone 11** au prix de **559€**.
+Les autres modèles disponibles en 128GB sont :
+*   iPhone 12 : 729€
+*   iPhone 13 : 809€
+*   iPhone 14 : 869€
+*   iPhone 15 : 969€
+*   iPhone 16 : 1019€
+L'iPhone X et l'iPhone 17 ne sont pas disponibles en version 128GB selon notre tableau de prix actuel.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -810,9 +850,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est identique à la réponse attendue et couvre tous les points essentiels (modèle, capacité, prix).</t>
+          <t>La réponse de l'agent est parfaitement conforme à la réponse attendue, identifiant correctement le modèle et le prix de l'iPhone le moins cher en 128GB. Les informations supplémentaires fournies sont pertinentes.</t>
         </is>
       </c>
     </row>
@@ -829,9 +867,9 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L'autonomie de l'iPhone 13 est jusqu'à 13h de lecture vidéo.
-L'autonomie de l'iPhone 16 est jusqu'à 22h de lecture vidéo.
-La différence d'autonomie entre l'iPhone 13 et l'iPhone 16 est de 9 heures (22h - 13h).</t>
+          <t>L'autonomie de l'iPhone 13 est jusqu'à 13 heures de lecture vidéo.
+L'autonomie de l'iPhone 16 est de 22 heures de lecture vidéo.
+La différence d'autonomie entre l'iPhone 16 et l'iPhone 13 est donc de **9 heures** en faveur de l'iPhone 16.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,9 +882,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: L'agent fournit une valeur correcte pour l'autonomie de l'iPhone 16 (22h, comme dans la réponse attendue) et tente de calculer la différence. Cependant, la valeur qu'il donne pour l'autonomie de l'iPhone 13 (13h) est incorrecte (l'iPhone 13 offre jusqu'à 19h de lecture vidéo), ce qui conduit à une différence finale erronée (9h au lieu de 3h).</t>
+          <t>L'agent indique correctement l'autonomie de l'iPhone 16 (22h), mais se trompe sur celle de l'iPhone 13 (13h au lieu de 19h). Cela conduit à une différence calculée de 9 heures, alors qu'elle devrait être de 3 heures.</t>
         </is>
       </c>
     </row>
@@ -863,7 +899,9 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oui, si vous êtes encore engagé, des frais de résiliation peuvent s'appliquer. Ces frais sont égaux au montant des mensualités restantes.</t>
+          <t>Oui, si vous êtes encore engagé, des frais de résiliation peuvent s'appliquer.
+Ces frais sont égaux au montant des mensualités restantes jusqu'à la fin de votre période d'engagement. Si vous êtes hors période d'engagement (après 12 ou 24 mois), la résiliation est gratuite.
+Pour connaître votre situation exacte et le montant éventuel des frais, nous vous invitons à consulter votre espace client ou à contacter le service client TelecomPlus au 3900 (appel gratuit, disponible 7j/7 de 8h à 20h).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,9 +914,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est correcte et couvre précisément la condition posée dans la question ("si je suis engagé"), en spécifiant qu'il y a des frais et qu'ils correspondent aux mensualités restantes. Bien que la réponse attendue offre un contexte supplémentaire sur la résiliation hors engagement, l'agent répond pleinement et précisément à la question posée.</t>
+          <t>La réponse de l'agent est complète et correcte, couvrant tous les points essentiels de la réponse attendue. Elle fournit même des informations supplémentaires utiles (comment vérifier sa situation et contacter le service client) qui ne sont pas dans la réponse attendue mais améliorent la réponse globale sans la dénaturer.</t>
         </is>
       </c>
     </row>
@@ -895,7 +931,9 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Votre consommation data pour le mois de novembre 2025 est de 3.2 Go utilisés sur les 5.0 Go inclus dans votre forfait. Il vous reste environ 1.80 Go.</t>
+          <t>Bonjour Jean Bertrand,
+D'après les dernières données disponibles, votre consommation data pour **novembre 2025** est de **3.2 Go utilisés sur les 5.0 Go** inclus dans votre forfait Essentiel 5GB. Il vous restait environ **1.80 Go**.
+Veuillez noter que ces données datent de novembre 2025. Pour consulter votre consommation la plus récente, nous vous invitons à vous connecter à votre espace client ou à contacter le service client au 3900.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,9 +946,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est complète et correcte. Elle fournit la consommation data et le forfait total, comme attendu, et ajoute même une information pertinente et utile sur le solde restant.</t>
+          <t>La réponse de l'agent est non seulement correcte et complète par rapport à la consommation data demandée (3.2 Go sur 5 Go), mais elle apporte également des informations supplémentaires très utiles, telles que le solde restant, la date de la consommation et les moyens de consulter des données plus récentes. La politesse est un plus.</t>
         </is>
       </c>
     </row>
@@ -927,7 +963,9 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monsieur Jean Bertrand, le montant de votre prochaine facture (mois de novembre 2025) est de 9.99 €.</t>
+          <t>Bonjour Jean Bertrand,
+Votre dernière facture disponible est celle du mois de **novembre 2025**. Le montant est de **9.99 €**. Elle est actuellement en statut "En attente" et sa date d'échéance était le 15 décembre 2025.
+Pour toute information complémentaire ou pour régler cette facture, vous pouvez vous connecter à votre Espace Client sur notre site web ou contacter le service client au 3900.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -936,13 +974,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: L'agent indique correctement le montant de la facture, mais omet la date d'échéance qui était attendue. Il mentionne le mois de la facture au lieu de la date d'échéance.</t>
+          <t>L'agent fournit le montant et la date d'échéance corrects qui correspondent à la demande de l'utilisateur pour sa "prochaine" facture à payer, même s'il utilise le terme "dernière facture disponible". L'information est pertinente et complète.</t>
         </is>
       </c>
     </row>
@@ -959,9 +995,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oui, vous avez deux tickets de support en cours :
-1.  **Ticket ID 4 :** Sujet "Débit très lent", créé le 2025-11-01.
-2.  **Ticket ID 3 :** Sujet "Frais de résiliation", créé le 2025-10-31.</t>
+          <t>Bonjour Monsieur Richard,
+Oui, vous avez actuellement deux tickets de support en cours :
+*   **Ticket ID 4 :** Sujet "Débit très lent", créé le 1er novembre 2025.
+*   **Ticket ID 3 :** Sujet "Frais de résiliation", créé le 31 octobre 2025.
+Les deux tickets ont un statut "En cours" et une priorité "Normale".</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,9 +1012,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est globalement correcte. Elle identifie correctement l'existence et le nombre de tickets, leurs ID et leurs sujets. Bien que les catégories entre parenthèses de la réponse attendue (Résiliation, Problème de réseau) soient omises, les sujets des tickets sont suffisamment explicites pour indiquer leur nature. L'ajout des dates de création est un détail pertinent et utile.</t>
+          <t>La réponse de l'agent est complète et correcte. Elle identifie les deux tickets en cours avec leurs sujets respectifs, et fournit même des détails supplémentaires pertinents (dates de création, statut, priorité) qui améliorent la réponse sans en altérer la justesse.</t>
         </is>
       </c>
     </row>
@@ -993,7 +1029,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Le coût d'un voyage de 2 semaines aux États-Unis n'est pas précisé dans le contexte fourni. Les coûts de roaming international varient selon le pays et le forfait. Des forfaits de roaming internationaux quotidiens et mensuels sont proposés pour gérer ces coûts.</t>
+          <t>Bonjour Jean Bertrand,
+Les États-Unis ne font pas partie de l'Union Européenne, par conséquent, des frais de roaming s'appliqueront pour votre voyage de 2 semaines.
+Les coûts du roaming international varient selon le pays et votre forfait. TelecomPlus propose des forfaits internationaux journaliers et mensuels pour vous aider à gérer ces coûts.
+Pour connaître le coût exact et les options de pass international adaptées à votre forfait pour votre voyage aux États-Unis, je vous recommande de :
+*   Consulter votre espace client sur [www.telecomplus.fr/mon-compte](www.telecomplus.fr/mon-compte) où vous pourrez voir les tarifs spécifiques et activer un pass.
+*   Contacter le Service Client TelecomPlus :
+    *   Par téléphone au 3900 (appel gratuit, disponible 7j/7 de 8h à 20h)
+    *   Par chat en ligne sur notre site web
+    *   Par email à support@telecomplus.fr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,9 +1050,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: L'agent explique correctement que le coût exact d'un voyage aux États-Unis n'est pas précisé sans plus de contexte, mais que les tarifs de roaming international varient selon le pays et le forfait. Il propose des forfaits de roaming internationaux quotidiens et mensuels, ce qui couvre la nature des solutions recommandées dans la réponse attendue (pass hebdomadaire ou journalier). La réponse est globalement correcte et fournit les informations essentielles pour comprendre le coût et les options disponibles.</t>
+          <t>La réponse de l'agent est excellente. Elle explique clairement pourquoi des frais de roaming s'appliqueront, indique que les coûts varient selon le forfait et propose des solutions (forfaits internationaux). Surtout, elle fournit des étapes claires et concrètes (consulter l'espace client, contacter le service client avec les différentes options) pour obtenir les informations personnalisées, ce qui est très utile pour l'utilisateur. La réponse attendue fait une supposition sur le forfait de l'utilisateur qui n'était pas dans la question, alors que l'agent gère cette incertitude de manière appropriée.</t>
         </is>
       </c>
     </row>
@@ -1025,8 +1067,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oui, Alexandre Martin, la résiliation de votre abonnement est gratuite car il est actuellement "Hors engagement".
-Vous pouvez résilier en envoyant une lettre recommandée avec accusé de réception ou via votre espace client en ligne.</t>
+          <t>Bonjour Alexandre,
+Oui, vous pouvez résilier votre abonnement sans frais.
+D'après nos informations, votre dernier abonnement (Forfait Confort 20GB) a débuté le 20/02/2024 avec un engagement de 12 mois. Cela signifie que votre période d'engagement s'est terminée en février 2025.
+Actuellement, vous êtes donc **hors période d'engagement**.
+**La résiliation est gratuite** si vous êtes hors période d'engagement, conformément à notre FAQ.
+Pour résilier, vous avez deux options :
+1.  Envoyer une lettre recommandée avec accusé de réception.
+2.  Passer par votre espace client en ligne.
+La résiliation prendra effet sous 10 jours à compter de la réception de votre demande.
+Si vous avez d'autres questions ou souhaitez de l'aide pour la démarche, n'hésitez pas à contacter notre Service Client au **3900** (appel gratuit, disponible 7j/7 de 8h à 20h).</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1039,9 +1089,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: L'agent répond correctement et directement à la question ("Oui, la résiliation est gratuite"). Il fournit la justification essentielle ("Hors engagement") qui est la conséquence des dates mentionnées dans la réponse attendue, et ajoute même des informations utiles sur les modalités de résiliation, ce qui est un plus. L'absence des dates spécifiques ne rend pas la réponse incorrecte ou partielle, car la raison fondamentale est donnée.</t>
+          <t>La réponse de l'agent est complète et correcte. Elle confirme la possibilité de résilier sans frais en justifiant l'absence de période d'engagement, ce qui correspond parfaitement à la réponse attendue. Elle fournit également des informations additionnelles utiles sur les modalités de résiliation.</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1106,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avec un budget de 1000€ pour un iPhone de 256GB, vous pouvez vous offrir les modèles suivants :
-*   **iPhone X (256GB)** à 749€
-*   **iPhone 11 (256GB)** à 659€
-*   **iPhone 12 (256GB)** à 829€
-*   **iPhone 13 (256GB)** à 929€
-*   **iPhone 14 (256GB)** à 999€</t>
+          <t>Avec votre budget de 1000€ pour un iPhone en version 256GB, voici les modèles que vous pouvez vous offrir, d'après notre catalogue mis à jour le 04/11/2025 :
+*   **iPhone X** (256GB) : 749€
+*   **iPhone 11** (256GB) : 659€
+*   **iPhone 12** (256GB) : 829€
+*   **iPhone 13** (256GB) : 929€
+*   **iPhone 14** (256GB) : 999€
+Les modèles suivants dépassent votre budget de 1000€ pour la version 256GB :
+*   L'iPhone 15 à 1099€
+*   L'iPhone 16 à 1149€
+*   L'iPhone 17 à 1299€
+Pour toute question ou pour passer commande, vous pouvez consulter notre site web ou contacter le service client au 3900.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1125,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: L'agent identifie correctement l'iPhone 14 (256GB) à 999€ comme une option, ce qui est le point essentiel de la réponse attendue et correcte. Cependant, il inclut également des modèles beaucoup plus anciens (iPhone X, 11, 12) avec des prix qui ne sont pas réalistes pour des appareils neufs et largement disponibles sur le marché actuel, ce qui rend une partie de la réponse trompeuse ou hors de propos pour l'achat d'un iPhone neuf.</t>
+          <t>La réponse de l'agent est complète et pertinente. Elle identifie correctement l'iPhone 14 comme une option et l'iPhone 15 comme hors budget, en accord avec la réponse attendue. De plus, elle propose plusieurs autres modèles (X, 11, 12, 13) qui respectent le budget et la capacité de stockage demandés, offrant ainsi plus de choix à l'utilisateur. La date future et les modèles 16/17 sont des détails contextuels qui n'altèrent pas la validité des options proposées pour le budget spécifié.</t>
         </is>
       </c>
     </row>
@@ -1095,9 +1146,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oui, vous pouvez utiliser votre forfait mobile en Italie, mais des frais de roaming et des tarifs internationaux s'appliqueront.
-Le contexte ne précise pas si des options spécifiques pour l'Italie sont incluses dans votre forfait Essentiel 5GB, ni si un changement est nécessaire pour votre séjour.
-Pour évaluer les options ou modifier votre forfait afin d'éviter des frais élevés, connectez-vous à votre espace client ou contactez le service client. Nous proposons également des forfaits d'appels internationaux.</t>
+          <t>Bonjour Jean Bertrand,
+Excellente nouvelle pour votre voyage en Italie !
+L'Italie fait partie de l'Union Européenne. Conformément à notre politique "roaming comme à la maison", **le roaming en Italie est gratuit et inclus dans votre forfait mobile TelecomPlus.**
+Vous n'avez donc **pas besoin de changer de forfait ou de prendre une option spécifique** pour votre séjour de 10 jours. Vous utiliserez votre forfait Essentiel 5GB (5 Go de data, appels et SMS illimités) comme si vous étiez en France, sans aucun surcoût.
+Si vous avez d'autres questions, n'hésitez pas à nous contacter :
+*   **Téléphone :** 3900 (appel gratuit, disponible 7j/7 de 8h à 20h)
+*   **Chat en ligne :** sur notre site web
+*   **Espace client :** www.telecomplus.fr/mon-compte</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,13 +1162,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Score: 0
-Label: incorrect
-Justification: La réponse de l'agent est fondamentalement incorrecte concernant les frais de roaming. Pour l'Italie, en tant que pays de l'UE, le roaming est généralement inclus sans surcoût ("roaming comme à la maison") pour les forfaits standards, comme indiqué dans la réponse attendue. L'agent indique à tort que des frais et tarifs internationaux s'appliqueront, ce qui est une information erronée et induirait le client en erreur.</t>
+          <t>L'agent fournit une réponse complète et correcte, expliquant clairement que le roaming en Italie est inclus dans le forfait existant de l'utilisateur, éliminant ainsi le besoin de changer de forfait ou de prendre une option. Les détails du forfait sont également mentionnés, correspondant à la réponse attendue.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1183,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oui, vous pouvez bénéficier d'une réduction en échangeant votre ancien téléphone lors de l'achat de l'iPhone 16.</t>
+          <t>Oui, vous pouvez bénéficier d'une réduction si vous rendez votre ancien iPhone. TelecomPlus propose un service de reprise qui vous permet d'échanger votre ancien téléphone et d'obtenir une réduction sur l'achat d'un nouveau modèle.
+Concernant l'iPhone 16, voici les prix disponibles :
+*   **iPhone 16 128GB :** 1019€
+*   **iPhone 16 256GB :** 1149€
+*   **iPhone 16 512GB :** 1409€
+Pour connaître le montant précis de la réduction applicable à votre ancien téléphone et pour finaliser l'achat de votre iPhone 16, nous vous invitons à :
+*   Contacter nos conseillers par téléphone au **3900** (appel gratuit).
+*   Vous rendre en boutique pour une évaluation de votre ancien appareil.
+*   Consulter notre site web **www.telecomplus.fr** pour plus de détails sur le processus de reprise.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1200,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: L'agent confirme correctement la possibilité de bénéficier d'une réduction en échangeant un ancien téléphone. Cependant, la réponse ne fournit pas les détails essentiels et les prochaines étapes (prix de l'iPhone, comment connaître la valeur de reprise, où se renseigner, canaux de contact) qui sont présents dans la réponse attendue et utiles à l'utilisateur.</t>
+          <t>La réponse de l'agent est excellente. Elle confirme la possibilité de la réduction, fournit les prix de l'iPhone 16 (y compris la version 128GB mentionnée dans la réponse attendue et des options supplémentaires), et indique clairement les différentes manières d'obtenir l'évaluation de l'ancien téléphone (téléphone, boutique, site web), couvrant ainsi tous les points essentiels et même plus.</t>
         </is>
       </c>
     </row>
@@ -1161,9 +1221,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Les iPhones suivants répondent à vos critères :
-*   **iPhone 15** (caméra principale 48 Mpx, 256GB, 1099€)
-*   **iPhone 16** (caméra Fusion 48 Mpx, 256GB, 1149€)</t>
+          <t>Pour un iPhone avec au moins 48 Mpx de caméra et 256GB de stockage, disponible pour moins de 1200€, nous avons un modèle qui correspond à vos critères :
+*   **iPhone 16 (2024)**
+    *   **Caméra :** Système de caméra Fusion 48 Mpx avec ultra grand-angle amélioré (ou caméra principale 48 Mpx).
+    *   **Stockage :** Disponible en 256GB.
+    *   **Prix 256GB :** 1149€.
+**Résumé des exclusions pour les autres modèles pertinents :**
+*   **iPhone X, iPhone 11, iPhone 12, iPhone 13, iPhone 14 :** Ces modèles sont équipés de caméras de 12 Mpx, ce qui ne répond pas à votre critère d'au moins 48 Mpx.
+*   **iPhone 15 :** Bien que son prix pour le 256GB soit de 1099€ (inférieur à 1200€), les informations fournies ne précisent pas une caméra d'au moins 48 Mpx.
+*   **iPhone 17 (2025) :** Il dispose d'une triple caméra 48 Mpx, mais son prix pour le 256GB est de 1299€, ce qui dépasse votre budget de 1200€.
+L'iPhone 16 est le seul modèle qui correspond parfaitement à votre recherche. Pour l'acheter, vous pouvez vous rendre sur notre site web, contacter le 3900, ou visiter votre espace client.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1172,13 +1239,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent identifie correctement les deux modèles d'iPhone qui répondent à tous les critères spécifiés (caméra 48 Mpx, 256GB, moins de 1200€), comme le faisait la réponse attendue. Elle couvre l'intégralité des points essentiels demandés.</t>
+          <t>L'agent a correctement identifié l'iPhone 16 comme une option valide et a exclu l'iPhone 17 pour son prix. Cependant, il a omis l'iPhone 15 qui, selon la réponse attendue et les spécifications réelles, dispose bien d'une caméra de 48 Mpx et respecte le budget et le stockage demandés.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1260,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Si vous passez au forfait supérieur conseillé, Confort 20GB, cela vous coûtera 6,00 € de plus par mois. Le nouveau forfait sera de 15,99 €/mois.</t>
+          <t>Bonjour Jean Bertrand,
+Actuellement, vous disposez du forfait **Essentiel 5GB** pour 9.99 € par mois, qui inclut 5.0 Go de data.
+Si vous souhaitez changer pour un forfait avec plus de data, nous vous conseillons le forfait **Confort 20GB** qui propose 20 Go de data pour 15.99 € par mois.
+Le surcoût mensuel de ce changement serait de **6.00 €**.
+Pour information, votre consommation la plus récente (novembre 2025) indique que vous avez utilisé 3.2 Go sur vos 5.0 Go inclus.
+Vous pouvez effectuer ce changement directement depuis votre Espace Client sur notre site web, ou en contactant le service client au 3900.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1204,13 +1274,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: La réponse de l'agent fournit correctement le coût supplémentaire et le prix du nouveau forfait. Cependant, elle omet l'identification du forfait actuel du client ainsi que les informations pratiques sur la manière de changer de forfait et la date d'effectivité, qui étaient présentes dans la réponse attendue et sont des points essentiels pour une réponse complète.</t>
+          <t>La réponse de l'agent est complète et correcte. Elle fournit tous les détails essentiels demandés concernant les forfaits et le coût supplémentaire. Bien qu'elle omette une information mineure sur la date d'effectivité du changement, elle ajoute des détails pertinents (consommation actuelle, autre méthode de contact) qui enrichissent la réponse.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1295,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D'après le contexte fourni, l'iPhone 17 est décrit avec une "triple caméra 48 Mpx avec périscope 5x et LiDAR", ce qui représente les caractéristiques photographiques les plus avancées mentionnées.</t>
+          <t>Selon les informations disponibles, l'iPhone le plus performant pour la photographie est l'**iPhone 17**.
+Il est équipé d'une **triple caméra 48 Mpx avec périscope 5x et LiDAR**, offrant les technologies les plus avancées pour la capture d'images.
+L'iPhone 17 (version 256GB) est proposé au prix de **1299€**.
+L'**iPhone 16** est également une excellente option avec sa **caméra Fusion 48 Mpx**, disponible à 1149€ pour la version 256GB. Il représente une alternative performante.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,13 +1307,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Score: 0.5
-Label: partial
-Justification: La réponse de l'agent identifie correctement l'iPhone 17 comme le meilleur pour la photographie et liste ses principales caractéristiques, ce qui correspond au point essentiel de la réponse attendue. Cependant, elle omet de mentionner l'iPhone 16 comme une excellente alternative et la nuance importante concernant le budget et les besoins spécifiques, qui sont tous deux inclus dans la réponse attendue.</t>
+          <t>La réponse de l'agent est excellente et couvre tous les points essentiels de la réponse attendue, en ajoutant même des détails pertinents comme les prix qui justifient la mention 'dépend de votre budget'.</t>
         </is>
       </c>
     </row>
@@ -1259,9 +1328,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oui, l'utilisation de votre iPhone à l'étranger sans surcoût dépend de la destination :
-*   **Dans l'Union Européenne (UE)** : Vous pouvez utiliser votre forfait français sans surcoût, selon les limites de votre contrat ("roaming comme à la maison").
-*   **Hors Europe** : Des frais de roaming s'appliquent. Pour les éviter, il est recommandé de désactiver les données mobiles et d'utiliser le WiFi, ou de souscrire à un pass international.</t>
+          <t>Oui, cela dépend de votre destination.
+*   **Dans l'Union Européenne (UE)** : Vous pouvez utiliser votre iPhone avec votre forfait français **sans surcoût**. C'est ce qu'on appelle le "roaming comme à la maison", selon les limites de votre contrat.
+*   **Hors de l'Union Européenne** : Des frais de roaming s'appliqueront. Pour éviter les frais, nous vous recommandons de désactiver les données mobiles et d'utiliser le Wi-Fi. Vous avez également la possibilité de souscrire un pass international (journalier ou hebdomadaire) via votre espace client.
+Le roaming international est généralement activé par défaut. Vous pouvez vérifier son statut et consulter les tarifs spécifiques à votre destination dans votre espace client ou en contactant le service client au 3900 (appel gratuit, disponible 7j/7 de 8h à 20h).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1274,9 +1344,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Score: 1
-Label: correct
-Justification: La réponse de l'agent est complète et correcte. Elle couvre tous les points essentiels de la réponse attendue et ajoute même une recommandation pertinente et utile (désactiver les données mobiles et utiliser le WiFi) pour les destinations hors Europe.</t>
+          <t>La réponse de l'agent est complète et correcte. Elle couvre tous les points de la réponse attendue et ajoute des informations complémentaires pertinentes et utiles pour l'utilisateur.</t>
         </is>
       </c>
     </row>
